--- a/output/pdf_financials_xlsx/IMPT.xlsx
+++ b/output/pdf_financials_xlsx/IMPT.xlsx
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.264756</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.01491</v>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.264756</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.01491</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14645,7 +14645,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">

--- a/output/pdf_financials_xlsx/IMPT.xlsx
+++ b/output/pdf_financials_xlsx/IMPT.xlsx
@@ -701,10 +701,10 @@
         <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.280317</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.280317</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>-0</v>
@@ -1029,10 +1029,10 @@
         <v>-10.555567</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>13.125437</v>
+        <v>12.84512</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-22.336913</v>
+        <v>-22.61723</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-5.254528</v>
@@ -1073,10 +1073,10 @@
         <v>-10.555567</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>12.934542</v>
+        <v>12.654225</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-22.402519</v>
+        <v>-22.682836</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-5.341053</v>
@@ -1097,10 +1097,10 @@
         <v>-134.4475813154012</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>223.3400035535369</v>
+        <v>218.4997858035681</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-605.7912813181185</v>
+        <v>-613.3713929388363</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -12252,7 +12252,11 @@
           <t>Debt financing costs 18</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -13451,7 +13455,11 @@
           <t>Debt financing costs</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IMPT.xlsx
+++ b/output/pdf_financials_xlsx/IMPT.xlsx
@@ -2616,7 +2616,7 @@
         <v>-0.090465</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-0.031452</v>
+        <v>-10.555567</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>13.125437</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.031374</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.453571</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.647797</v>
       </c>
     </row>
     <row r="111">
@@ -6551,7 +6551,11 @@
           <t>Deferred tax recovery 23</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -6789,7 +6793,11 @@
           <t>Accretion expense 18</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -7919,7 +7927,11 @@
           <t>Net Income (loss) $</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -8282,7 +8294,11 @@
           <t>Accretion expense 22</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -10227,7 +10243,11 @@
           <t>Share based payments expense</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E168" s="5" t="n">
         <v>0.015687</v>
       </c>
@@ -10776,7 +10796,11 @@
           <t>Share based payment expense - - 15,687</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E181" s="5" t="n">
         <v>0.015687</v>
       </c>
@@ -10981,7 +11005,11 @@
           <t>Share based payments expense</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E186" s="5" t="n">
         <v>0.015687</v>
       </c>
@@ -11321,7 +11349,11 @@
           <t>Share based payment expense - - 15,687</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E194" s="5" t="n">
         <v>0.015687</v>
       </c>
